--- a/SGC-CKN/Excel/f249a2a1-47b3-4339-aae0-5f4f22c46144_Thanh_Hoá_P7_61_D800_02-04-2026.xlsx
+++ b/SGC-CKN/Excel/f249a2a1-47b3-4339-aae0-5f4f22c46144_Thanh_Hoá_P7_61_D800_02-04-2026.xlsx
@@ -1347,16 +1347,16 @@
         <v>-17.28</v>
       </c>
       <c r="G14" s="15">
-        <v>-21.57</v>
+        <v>-21.52</v>
       </c>
       <c r="H14" s="15">
         <v>0.78</v>
       </c>
       <c r="I14" s="15">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="J14" s="8">
-        <v>5.48</v>
+        <v>5.41</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>35</v>
@@ -1379,7 +1379,7 @@
         <v>47</v>
       </c>
       <c r="F15" s="18">
-        <v>-21.57</v>
+        <v>-21.52</v>
       </c>
       <c r="G15" s="18">
         <v>-25.52</v>
@@ -1388,10 +1388,10 @@
         <v>0.73</v>
       </c>
       <c r="I15" s="18">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J15" s="8">
-        <v>5.39</v>
+        <v>5.45</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>35</v>
@@ -1452,16 +1452,16 @@
         <v>-35.52</v>
       </c>
       <c r="G17" s="24">
-        <v>-37.9</v>
+        <v>-37.4</v>
       </c>
       <c r="H17" s="24">
         <v>1.28</v>
       </c>
       <c r="I17" s="24">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="J17" s="27">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>35</v>
@@ -1484,19 +1484,19 @@
         <v>59</v>
       </c>
       <c r="F18" s="28">
-        <v>-37.9</v>
+        <v>-37.4</v>
       </c>
       <c r="G18" s="28">
-        <v>-41.2</v>
+        <v>-40</v>
       </c>
       <c r="H18" s="28">
         <v>0.37</v>
       </c>
       <c r="I18" s="28">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J18" s="8">
-        <v>9</v>
+        <v>7.09</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>60</v>
@@ -1519,7 +1519,7 @@
         <v>63</v>
       </c>
       <c r="F19" s="31">
-        <v>-41.2</v>
+        <v>-40</v>
       </c>
       <c r="G19" s="31">
         <v>-43.2</v>
@@ -1528,10 +1528,10 @@
         <v>1</v>
       </c>
       <c r="I19" s="31">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J19" s="27">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>35</v>
@@ -1811,16 +1811,16 @@
         <v>-17.28</v>
       </c>
       <c r="F5" s="15">
-        <v>-21.57</v>
+        <v>-21.52</v>
       </c>
       <c r="G5" s="15">
         <v>0.78</v>
       </c>
       <c r="H5" s="15">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="I5" s="8">
-        <v>5.48</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1837,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>-21.57</v>
+        <v>-21.52</v>
       </c>
       <c r="F6" s="18">
         <v>-25.52</v>
@@ -1846,10 +1846,10 @@
         <v>0.73</v>
       </c>
       <c r="H6" s="18">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I6" s="8">
-        <v>5.39</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1898,16 +1898,16 @@
         <v>-35.52</v>
       </c>
       <c r="F8" s="24">
-        <v>-37.9</v>
+        <v>-37.4</v>
       </c>
       <c r="G8" s="24">
         <v>1.28</v>
       </c>
       <c r="H8" s="24">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="I8" s="27">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1924,19 +1924,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-37.9</v>
+        <v>-37.4</v>
       </c>
       <c r="F9" s="28">
-        <v>-41.2</v>
+        <v>-40</v>
       </c>
       <c r="G9" s="28">
         <v>0.37</v>
       </c>
       <c r="H9" s="28">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="I9" s="8">
-        <v>9</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1953,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-41.2</v>
+        <v>-40</v>
       </c>
       <c r="F10" s="31">
         <v>-43.2</v>
@@ -1962,10 +1962,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="31">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="I10" s="27">
-        <v>2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
